--- a/Utiles/exceljs.xlsx
+++ b/Utiles/exceljs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>S No:</t>
   </si>
@@ -40,10 +40,10 @@
     <t>Android</t>
   </si>
   <si>
+    <t>sony</t>
+  </si>
+  <si>
     <t>Redmi</t>
-  </si>
-  <si>
-    <t>EMUI</t>
   </si>
 </sst>
 </file>
@@ -467,8 +467,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>50000</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
         <v>52000</v>
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>55000</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
